--- a/trach_data/Train Measurements.xlsx
+++ b/trach_data/Train Measurements.xlsx
@@ -1,110 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">Train Speed Summary — Average Observed Speed by Track Type &amp; Speed Step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed Step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg Observed Speed (us/mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large Curved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Straight</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="8">
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
+      <charset val="1"/>
       <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
+      <charset val="1"/>
       <family val="0"/>
-      <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="1"/>
       <family val="0"/>
-      <charset val="1"/>
+      <i val="1"/>
+      <color rgb="FF999999"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i val="true"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
       <sz val="10"/>
-      <color rgb="FF999999"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -141,14 +112,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="medium">
         <color rgb="FF1F4E79"/>
       </left>
@@ -163,7 +134,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBBBBBB"/>
       </left>
@@ -179,92 +150,101 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -502,341 +482,404 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col width="18" customWidth="1" style="13" min="1" max="1"/>
+    <col width="14" customWidth="1" style="13" min="2" max="2"/>
+    <col width="30" customWidth="1" style="13" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="1" ht="27.75" customHeight="1" s="14">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Train Speed Summary — Average Observed Speed by Track Type &amp; Speed Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="14">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Track Type</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Speed Step</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Avg Observed Speed (us/mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="14">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C3" s="19" t="n">
+        <v>25160.7009</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="14">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>48700.8933</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="14">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C5" s="19" t="n">
+        <v>20585.6288</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="14">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>31292.3456</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="14">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="C7" s="22" t="n">
+        <v>15601.252</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="14">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>20001.7925</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="14">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>15601.252</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="C9" s="25" t="n">
+        <v>12701.003</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="14">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>13001.1875</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="14">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>20001.7925</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>15601.252</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="C11" s="22" t="n">
+        <v>8400.804</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="14">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>20001.7925</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>15601.252</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>20001.7925</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>12701.003</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>13001.1875</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>8400.804</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="22" t="n">
         <v>8500.731</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="11" t="n">
+    <row r="13" ht="18" customHeight="1" s="14">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="25" t="n">
         <v>6080.4016</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="11" t="n">
+    <row r="14" ht="18" customHeight="1" s="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="25" t="n">
         <v>6167.2663</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="8" t="n">
+    <row r="15" ht="18" customHeight="1" s="14">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="22" t="n">
         <v>4533.6503</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="8" t="n">
+    <row r="16" ht="18" customHeight="1" s="14">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="22" t="n">
         <v>4500.3025</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="11" t="n">
+    <row r="17" ht="18" customHeight="1" s="14">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="25" t="n">
         <v>3480.3804</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="11" t="n">
+    <row r="18" ht="18" customHeight="1" s="14">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="25" t="n">
         <v>3464.5693</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="8" t="n">
+    <row r="19" ht="18" customHeight="1" s="14">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="22" t="n">
         <v>2766.9333</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="8" t="n">
+    <row r="20" ht="18" customHeight="1" s="14">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="22" t="n">
         <v>2781.5619</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="11" t="n">
+    <row r="21" ht="18" customHeight="1" s="14">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="25" t="n">
         <v>2280.26</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="11" t="n">
+    <row r="22" ht="18" customHeight="1" s="14">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="25" t="n">
         <v>2250.2411</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="8" t="n">
+    <row r="23" ht="18" customHeight="1" s="14">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="22" t="n">
         <v>1833.4337</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="8" t="n">
+    <row r="24" ht="18" customHeight="1" s="14">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="22" t="n">
         <v>1821.5511</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="11" t="n">
+    <row r="25" ht="18" customHeight="1" s="14">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="25" t="n">
         <v>1600.203</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="11" t="n">
+    <row r="26" ht="18" customHeight="1" s="14">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="25" t="n">
         <v>1607.3246</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8" t="n">
+    <row r="27" ht="18" customHeight="1" s="14">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="22" t="n">
         <v>1375.1582</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="8" t="n">
+    <row r="28" ht="18" customHeight="1" s="14">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="22" t="n">
         <v>1324.966</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="11" t="n">
+    <row r="29" ht="18" customHeight="1" s="14">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Large Curved</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="25" t="n">
         <v>1199.9838</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="11" t="n">
+    <row r="30" ht="15" customHeight="1" s="14">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="25" t="n">
         <v>1150.1527</v>
       </c>
     </row>
@@ -844,12 +887,8 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>